--- a/output/roomself_excel/14457.xlsx
+++ b/output/roomself_excel/14457.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>447101</v>
+        <v>96814</v>
       </c>
       <c r="D2" t="n">
-        <v>7912</v>
+        <v>2564</v>
       </c>
       <c r="E2" t="n">
-        <v>1210</v>
+        <v>382</v>
       </c>
       <c r="F2" t="n">
-        <v>663</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>117381</v>
+        <v>258042</v>
       </c>
       <c r="D3" t="n">
-        <v>3140</v>
+        <v>4128</v>
       </c>
       <c r="E3" t="n">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="F3" t="n">
-        <v>240</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>137082</v>
+        <v>110284</v>
       </c>
       <c r="D4" t="n">
-        <v>4996</v>
+        <v>2660</v>
       </c>
       <c r="E4" t="n">
-        <v>665</v>
+        <v>349</v>
       </c>
       <c r="F4" t="n">
-        <v>549</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>110284</v>
+        <v>205446</v>
       </c>
       <c r="D5" t="n">
-        <v>2660</v>
+        <v>3740</v>
       </c>
       <c r="E5" t="n">
-        <v>349</v>
+        <v>665</v>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>205446</v>
+        <v>53313</v>
       </c>
       <c r="D8" t="n">
-        <v>3740</v>
+        <v>2024</v>
       </c>
       <c r="E8" t="n">
-        <v>665</v>
+        <v>225</v>
       </c>
       <c r="F8" t="n">
-        <v>394</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>73472</v>
+        <v>137082</v>
       </c>
       <c r="D9" t="n">
-        <v>2172</v>
+        <v>4996</v>
       </c>
       <c r="E9" t="n">
-        <v>662</v>
+        <v>549</v>
       </c>
       <c r="F9" t="n">
-        <v>327</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>177597</v>
+        <v>92245</v>
       </c>
       <c r="D10" t="n">
-        <v>5380</v>
+        <v>3428</v>
       </c>
       <c r="E10" t="n">
-        <v>932</v>
+        <v>712</v>
       </c>
       <c r="F10" t="n">
-        <v>731</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>43020</v>
+        <v>62527</v>
       </c>
       <c r="D11" t="n">
-        <v>1676</v>
+        <v>2048</v>
       </c>
       <c r="E11" t="n">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="F11" t="n">
-        <v>215</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>53313</v>
+        <v>60705</v>
       </c>
       <c r="D12" t="n">
-        <v>2024</v>
+        <v>1992</v>
       </c>
       <c r="E12" t="n">
-        <v>225</v>
+        <v>362</v>
       </c>
       <c r="F12" t="n">
-        <v>79</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>62527</v>
+        <v>34704</v>
       </c>
       <c r="D13" t="n">
-        <v>2048</v>
+        <v>1540</v>
       </c>
       <c r="E13" t="n">
-        <v>553</v>
+        <v>311</v>
       </c>
       <c r="F13" t="n">
-        <v>345</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>39581</v>
+        <v>117381</v>
       </c>
       <c r="D14" t="n">
-        <v>2008</v>
+        <v>3140</v>
       </c>
       <c r="E14" t="n">
-        <v>171</v>
+        <v>666</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>61502</v>
+        <v>73472</v>
       </c>
       <c r="D15" t="n">
-        <v>2156</v>
+        <v>2172</v>
       </c>
       <c r="E15" t="n">
-        <v>610</v>
+        <v>336</v>
       </c>
       <c r="F15" t="n">
-        <v>262</v>
+        <v>327</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>60705</v>
+        <v>177597</v>
       </c>
       <c r="D16" t="n">
-        <v>1992</v>
+        <v>5380</v>
       </c>
       <c r="E16" t="n">
-        <v>610</v>
+        <v>731</v>
       </c>
       <c r="F16" t="n">
-        <v>362</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,64 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>34704</v>
+        <v>43020</v>
       </c>
       <c r="D17" t="n">
-        <v>1540</v>
+        <v>1676</v>
       </c>
       <c r="E17" t="n">
-        <v>610</v>
+        <v>276</v>
       </c>
       <c r="F17" t="n">
-        <v>179</v>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>39581</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E18" t="n">
+        <v>171</v>
+      </c>
+      <c r="F18" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>61502</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2156</v>
+      </c>
+      <c r="E19" t="n">
+        <v>262</v>
+      </c>
+      <c r="F19" t="n">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/14457.xlsx
+++ b/output/roomself_excel/14457.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,26 @@
       <c r="D2" t="n">
         <v>2564</v>
       </c>
-      <c r="E2" t="n">
-        <v>382</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +561,42 @@
       <c r="D3" t="n">
         <v>4128</v>
       </c>
-      <c r="E3" t="n">
-        <v>663</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>615</v>
-      </c>
+        <v>585</v>
+      </c>
+      <c r="G3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>379</v>
+      </c>
+      <c r="J3" t="n">
+        <v>38</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>447</v>
+      </c>
+      <c r="M3" t="n">
+        <v>40</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +613,26 @@
       <c r="D4" t="n">
         <v>2660</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>349</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>42</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +649,42 @@
       <c r="D5" t="n">
         <v>3740</v>
       </c>
-      <c r="E5" t="n">
-        <v>665</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>394</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="G5" t="n">
+        <v>41</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>353</v>
+      </c>
+      <c r="J5" t="n">
+        <v>42</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>582</v>
+      </c>
+      <c r="M5" t="n">
+        <v>41</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +701,26 @@
       <c r="D6" t="n">
         <v>1528</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>186</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>42</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +737,42 @@
       <c r="D7" t="n">
         <v>1548</v>
       </c>
-      <c r="E7" t="n">
-        <v>400</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>191</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>235</v>
+      </c>
+      <c r="J7" t="n">
+        <v>39</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>78</v>
+      </c>
+      <c r="M7" t="n">
+        <v>39</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +789,26 @@
       <c r="D8" t="n">
         <v>2024</v>
       </c>
-      <c r="E8" t="n">
-        <v>225</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>79</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="G8" t="n">
+        <v>37</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +825,42 @@
       <c r="D9" t="n">
         <v>4996</v>
       </c>
-      <c r="E9" t="n">
-        <v>549</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
+        <v>182</v>
+      </c>
+      <c r="G9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>186</v>
       </c>
+      <c r="M9" t="n">
+        <v>41</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +877,34 @@
       <c r="D10" t="n">
         <v>3428</v>
       </c>
-      <c r="E10" t="n">
-        <v>712</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>348</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>183</v>
+      </c>
+      <c r="J10" t="n">
+        <v>39</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +921,34 @@
       <c r="D11" t="n">
         <v>2048</v>
       </c>
-      <c r="E11" t="n">
-        <v>322</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>272</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="G11" t="n">
+        <v>35</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>202</v>
+      </c>
+      <c r="J11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +965,34 @@
       <c r="D12" t="n">
         <v>1992</v>
       </c>
-      <c r="E12" t="n">
-        <v>362</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>320</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="G12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>264</v>
+      </c>
+      <c r="J12" t="n">
+        <v>37</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +1009,34 @@
       <c r="D13" t="n">
         <v>1540</v>
       </c>
-      <c r="E13" t="n">
-        <v>311</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>179</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="G13" t="n">
+        <v>35</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>241</v>
+      </c>
+      <c r="J13" t="n">
+        <v>35</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +1053,42 @@
       <c r="D14" t="n">
         <v>3140</v>
       </c>
-      <c r="E14" t="n">
-        <v>666</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>240</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="G14" t="n">
+        <v>39</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>183</v>
+      </c>
+      <c r="J14" t="n">
+        <v>40</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>201</v>
+      </c>
+      <c r="M14" t="n">
+        <v>42</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1105,34 @@
       <c r="D15" t="n">
         <v>2172</v>
       </c>
-      <c r="E15" t="n">
-        <v>336</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>327</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="G15" t="n">
+        <v>40</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>256</v>
+      </c>
+      <c r="J15" t="n">
+        <v>40</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,11 +1149,49 @@
       <c r="D16" t="n">
         <v>5380</v>
       </c>
-      <c r="E16" t="n">
-        <v>731</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>320</v>
+        <v>150</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>275</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>136</v>
+      </c>
+      <c r="M16" t="n">
+        <v>35</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>149</v>
+      </c>
+      <c r="P16" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -805,12 +1209,34 @@
       <c r="D17" t="n">
         <v>1676</v>
       </c>
-      <c r="E17" t="n">
-        <v>276</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>215</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="G17" t="n">
+        <v>35</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>180</v>
+      </c>
+      <c r="J17" t="n">
+        <v>37</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1253,26 @@
       <c r="D18" t="n">
         <v>2008</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>171</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>37</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1289,34 @@
       <c r="D19" t="n">
         <v>2156</v>
       </c>
-      <c r="E19" t="n">
-        <v>262</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>73</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="G19" t="n">
+        <v>37</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>108</v>
+      </c>
+      <c r="J19" t="n">
+        <v>35</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
